--- a/pdf2img/hasil_ekstraksi/table_10/tabel_1.xlsx
+++ b/pdf2img/hasil_ekstraksi/table_10/tabel_1.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LAPORAN KOMITMEN DAN KONTINJENSI Per 31 Desember 202s dan 31 Desember 2024</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LAPORAN KOMITMEN DAN KONTINJENSI Per 31 Desember 202s dan 31 Desember 2024</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LAPORAN KOMITMEN DAN KONTINJENSI Per 31 Desember 202s dan 31 Desember 2024</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LAPORAN KOMITMEN DAN KONTINJENSI Per 31 Desember 202s dan 31 Desember 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>POS.POS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>31.0es.25</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>31.0es.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1 3 IL. a Commtted Uncommned 3 4 Lamrya 二 TAGIHAN KONTINJENSI Garans yang chermma Lanrya V KEWAJIBAN KONTINJENSI Garans yang cberkan Lamya</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TAGIHAN KOMITMEN Fasl as prpamar pembayaan yang beun dark. Poss valas yang aan drerma dan ransaks spot dan cormat fonward Lamrya KEWAJIBAN KOMITMEN Fasl as bed pemoayaan yang belu m dtank Irevocabie UC yang mas.h beralan Poss valas yang akan dserahkan Jr'ua transaus spot car Cervat lorward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4 485 629 22 09.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4024 4 129 909 277816 479 926 231 933</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf2img/hasil_ekstraksi/table_10/tabel_1.xlsx
+++ b/pdf2img/hasil_ekstraksi/table_10/tabel_1.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw_extraction" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cleaned_output" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,15 +30,21 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+        <bgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -51,14 +58,34 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,95 +452,583 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:B125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Be 20</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>M</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr"/>
+      <c r="B29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr"/>
+      <c r="B31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr"/>
+      <c r="B33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr"/>
+      <c r="B34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr"/>
+      <c r="B35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr"/>
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr"/>
+      <c r="B37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr"/>
+      <c r="B38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr"/>
+      <c r="B39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr"/>
+      <c r="B40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr"/>
+      <c r="B41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr"/>
+      <c r="B42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr"/>
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr"/>
+      <c r="B44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr"/>
+      <c r="B45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr"/>
+      <c r="B46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr"/>
+      <c r="B47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr"/>
+      <c r="B48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr"/>
+      <c r="B49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr"/>
+      <c r="B50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr"/>
+      <c r="B51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr"/>
+      <c r="B52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr"/>
+      <c r="B53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr"/>
+      <c r="B54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr"/>
+      <c r="B55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr"/>
+      <c r="B56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr"/>
+      <c r="B57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr"/>
+      <c r="B58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr"/>
+      <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>M</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr"/>
+      <c r="B60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr"/>
+      <c r="B61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr"/>
+      <c r="B62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr"/>
+      <c r="B63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr"/>
+      <c r="B64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr"/>
+      <c r="B65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr"/>
+      <c r="B66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr"/>
+      <c r="B67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr"/>
+      <c r="B68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr"/>
+      <c r="B69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr"/>
+      <c r="B70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr"/>
+      <c r="B71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr"/>
+      <c r="B72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr"/>
+      <c r="B73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr"/>
+      <c r="B74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr"/>
+      <c r="B75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr"/>
+      <c r="B76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr"/>
+      <c r="B77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr"/>
+      <c r="B78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr"/>
+      <c r="B79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr"/>
+      <c r="B80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr"/>
+      <c r="B81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr"/>
+      <c r="B82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr"/>
+      <c r="B83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr"/>
+      <c r="B84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr"/>
+      <c r="B85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr"/>
+      <c r="B86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr"/>
+      <c r="B87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr"/>
+      <c r="B88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr"/>
+      <c r="B89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr"/>
+      <c r="B90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr"/>
+      <c r="B91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr"/>
+      <c r="B92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr"/>
+      <c r="B93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr"/>
+      <c r="B94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr"/>
+      <c r="B95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr"/>
+      <c r="B96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr"/>
+      <c r="B97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr"/>
+      <c r="B98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr"/>
+      <c r="B99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr"/>
+      <c r="B100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr"/>
+      <c r="B101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr"/>
+      <c r="B102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr"/>
+      <c r="B103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr"/>
+      <c r="B104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr"/>
+      <c r="B105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr"/>
+      <c r="B106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr"/>
+      <c r="B107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr"/>
+      <c r="B108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr"/>
+      <c r="B109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr"/>
+      <c r="B110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr"/>
+      <c r="B111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr"/>
+      <c r="B112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr"/>
+      <c r="B113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr"/>
+      <c r="B114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr"/>
+      <c r="B115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr"/>
+      <c r="B116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr"/>
+      <c r="B117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr"/>
+      <c r="B118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr"/>
+      <c r="B119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr"/>
+      <c r="B120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr"/>
+      <c r="B121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr"/>
+      <c r="B122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr"/>
+      <c r="B123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr"/>
+      <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>LAPORAN KOMITMEN DAN KONTINJENSI Per 31 Desember 202s dan 31 Desember 2024</t>
+          <t>8</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr"/>
+      <c r="B125" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>LAPORAN KOMITMEN DAN KONTINJENSI Per 31 Desember 202s dan 31 Desember 2024</t>
+          <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>LAPORAN KOMITMEN DAN KONTINJENSI Per 31 Desember 202s dan 31 Desember 2024</t>
+          <t>Be 20</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>LAPORAN KOMITMEN DAN KONTINJENSI Per 31 Desember 202s dan 31 Desember 2024</t>
+          <t>M</t>
         </is>
       </c>
+      <c r="B2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>M</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>POS.POS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>31.0es.25</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>31.0es.24</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1 3 IL. a Commtted Uncommned 3 4 Lamrya 二 TAGIHAN KONTINJENSI Garans yang chermma Lanrya V KEWAJIBAN KONTINJENSI Garans yang cberkan Lamya</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TAGIHAN KOMITMEN Fasl as prpamar pembayaan yang beun dark. Poss valas yang aan drerma dan ransaks spot dan cormat fonward Lamrya KEWAJIBAN KOMITMEN Fasl as bed pemoayaan yang belu m dtank Irevocabie UC yang mas.h beralan Poss valas yang akan dserahkan Jr'ua transaus spot car Cervat lorward</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>4 485 629 22 09.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4024 4 129 909 277816 479 926 231 933</t>
-        </is>
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/pdf2img/hasil_ekstraksi/table_10/tabel_1.xlsx
+++ b/pdf2img/hasil_ekstraksi/table_10/tabel_1.xlsx
@@ -993,19 +993,19 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>column</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Be 20</t>
+          <t>column_2</t>
         </is>
       </c>
     </row>
